--- a/data/primes.xlsx
+++ b/data/primes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,43 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2893913171</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>reda affelad</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>prima 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
